--- a/prodotti/budget-familiare/Budget_Familiare_2027.xlsx
+++ b/prodotti/budget-familiare/Budget_Familiare_2027.xlsx
@@ -60,6 +60,9 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
 </styleSheet>
 </file>
 
